--- a/網站盤點表-中文.xlsx
+++ b/網站盤點表-中文.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="中文" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -398,14 +398,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F60"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="60.83203125" customWidth="1"/>
-    <col min="3" max="3" width="50.83203125" customWidth="1"/>
-    <col min="4" max="4" width="60.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="50.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -515,10 +507,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=E6309CCCA6ED1775</v>
       </c>
       <c r="C6" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議修正】相關檔案「111年外國專業人才延攬及僱用相關法規彙編」標示(待更新)，已歷時約4年未更新，建議儘速更新為最新版本（含115年1月1日施行之修正條文）。</v>
       </c>
       <c r="D6" t="str">
-        <v>已檢視認識本法頁面；含外國人才專法沿革及全文連結，建議於修法後更新說明文字。</v>
+        <v>頁面說明外國人才專法立法沿革、修法重點，內文已涵蓋2025年第二次修法內容，內容正確。惟相關檔案「111年法規彙編」仍標示待更新，應更新為最新彙編版本。</v>
       </c>
       <c r="E6" t="str">
         <v>每半年</v>
@@ -678,7 +670,7 @@
         <v>建議於大學排名更新時同步檢視資格條件。</v>
       </c>
       <c r="D14" t="str">
-        <v>已檢視碩士及前1,500大畢業生免2年工作經驗頁面；建議於大學排名更新時檢視。</v>
+        <v>說明2025修法後放寬至前1,500大畢業生可免2年工作經驗之規定。</v>
       </c>
       <c r="E14" t="str">
         <v>每年</v>
@@ -735,7 +727,7 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=C6219BB014315D72</v>
       </c>
       <c r="C17" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議定期確認】收費標準如有調整，應及時更新。</v>
       </c>
       <c r="D17" t="str">
         <v>已檢視工作許可收費標準頁面；建議於費率調整時同步更新。</v>
@@ -775,10 +767,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=C5FB0824CEC076D8</v>
       </c>
       <c r="C19" t="str">
-        <v>建議每月更新統計數據及確認申請說明是否需調整。</v>
+        <v>【建議修正】相關檔案「就業金卡申辦流程」PDF顯示日期為20211019，已超過4年未更新，應更新至現行版本（含115年修法後之申辦方式）。</v>
       </c>
       <c r="D19" t="str">
-        <v>已檢視就業金卡頁面；含申請說明與統計資料，建議每月更新統計數據。</v>
+        <v>就業金卡頁面說明申辦方式，並連結至就業金卡官方網站及申辦窗口平台，惟所附申辦流程PDF日期偏舊，需更新。</v>
       </c>
       <c r="E19" t="str">
         <v>每季</v>
@@ -915,10 +907,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=1384836FA7D2CFA6</v>
       </c>
       <c r="C26" t="str">
-        <v>建議定期檢視Q&amp;A內容是否需要依修法更新。</v>
+        <v>【建議確認】修法後應確認Q&amp;A各子項是否已更新至115年修法內容。</v>
       </c>
       <c r="D26" t="str">
-        <v>已檢視Q&amp;A總覽頁面；為各分類常見問題之入口頁。</v>
+        <v>頁面分為「關於本法」及「工作/尋職/數位遊牧」等多個分類，內含多個子頁面。2025修法後應定期確認各Q&amp;A內容是否與現行規定一致。</v>
       </c>
       <c r="E26" t="str">
         <v>每半年</v>

--- a/網站盤點表-中文.xlsx
+++ b/網站盤點表-中文.xlsx
@@ -447,10 +447,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Default.aspx</v>
       </c>
       <c r="C3" t="str">
-        <v>建議定期檢查首頁最新消息與相關連結之有效性。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D3" t="str">
-        <v>已檢視首頁公開頁面；首頁含最新消息、相關連結等區塊，內容正常顯示。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E3" t="str">
         <v>每季</v>
@@ -487,10 +487,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/News.aspx?n=801CA6E93C4EF61B&amp;sms=39B785FD08C5E6BB</v>
       </c>
       <c r="C5" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議維護】定期檢視過期消息是否需歸檔，並發布最新修法動態。</v>
       </c>
       <c r="D5" t="str">
-        <v>已檢視最新消息頁面；包含就業金卡統計及修法公告等，建議定期更新。</v>
+        <v>最新消息列表正常，建議持續發布相關政策宣導資訊。</v>
       </c>
       <c r="E5" t="str">
         <v>每月</v>
@@ -527,10 +527,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=428F82FDFFD8D145</v>
       </c>
       <c r="C7" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視宣導素材（懶人包/摺頁）是否符合最新法規（115年施行），舊版建議標示或下架。</v>
       </c>
       <c r="D7" t="str">
-        <v>已檢視宣導資料頁面；含宣傳文件，建議定期補充最新宣導素材。</v>
+        <v>頁面包含各式宣導資料，建議確認內容是否與現行法規一致。</v>
       </c>
       <c r="E7" t="str">
         <v>每季</v>
@@ -547,10 +547,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=8E20BBA0AFD356E5</v>
       </c>
       <c r="C8" t="str">
-        <v>建議於修法通過後更新附件檔案與說明內容。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D8" t="str">
-        <v>已檢視2025修法頁面；含修法重點與附件下載，建議於修法後確認附件是否為最新版本。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E8" t="str">
         <v>每季</v>
@@ -567,10 +567,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=80F66FE209D27DBA</v>
       </c>
       <c r="C9" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D9" t="str">
-        <v>已檢視子法及配套措施總覽頁面；為各子項目之入口頁，建議確認子項連結皆正常。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E9" t="str">
         <v>每半年</v>
@@ -587,10 +587,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=398B18EC2B34D6FC</v>
       </c>
       <c r="C10" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D10" t="str">
-        <v>已檢視該公開頁面內容。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E10" t="str">
         <v>每半年</v>
@@ -607,10 +607,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=83A1B1418636FA8A</v>
       </c>
       <c r="C11" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D11" t="str">
-        <v>已檢視教師相關工作許可頁面；含申請條件與法規連結。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E11" t="str">
         <v>每半年</v>
@@ -627,10 +627,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=F697A748D7F5D7D9</v>
       </c>
       <c r="C12" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D12" t="str">
-        <v>已檢視教師相關工作許可頁面；含申請條件與法規連結。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E12" t="str">
         <v>每半年</v>
@@ -647,10 +647,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=6B41A78BC745C459</v>
       </c>
       <c r="C13" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D13" t="str">
-        <v>已檢視實驗教育工作者頁面；含申請條件說明。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E13" t="str">
         <v>每半年</v>
@@ -667,7 +667,7 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=2369F40A62F27FA1</v>
       </c>
       <c r="C14" t="str">
-        <v>建議於大學排名更新時同步檢視資格條件。</v>
+        <v>【建議檢視】建議檢視頁面連結有效性，並確認是否符合放寬後之規定。</v>
       </c>
       <c r="D14" t="str">
         <v>說明2025修法後放寬至前1,500大畢業生可免2年工作經驗之規定。</v>
@@ -687,10 +687,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=DAE420E146D0F993</v>
       </c>
       <c r="C15" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D15" t="str">
-        <v>已檢視自由藝術工作者頁面；含申請條件說明。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E15" t="str">
         <v>每半年</v>
@@ -707,10 +707,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=C4F01439FC9E3E34</v>
       </c>
       <c r="C16" t="str">
-        <v>建議於大學排名更新時同步檢視資格條件。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D16" t="str">
-        <v>已檢視前200大畢業生個人工作許可頁面；建議於大學排名更新時檢視。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E16" t="str">
         <v>每年</v>
@@ -730,7 +730,7 @@
         <v>【建議定期確認】收費標準如有調整，應及時更新。</v>
       </c>
       <c r="D17" t="str">
-        <v>已檢視工作許可收費標準頁面；建議於費率調整時同步更新。</v>
+        <v>頁面說明各類工作許可收費標準，建議確認金額是否與勞動部公告一致。</v>
       </c>
       <c r="E17" t="str">
         <v>每年</v>
@@ -747,10 +747,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/cp.aspx?n=D5BE87506A7C6242&amp;s=9EABA5E27250AC15</v>
       </c>
       <c r="C18" t="str">
-        <v>建議定期檢查各領域認定標準之外部連結有效性。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D18" t="str">
-        <v>已檢視特定專業人才頁面；含各領域認定標準與外部連結，建議定期檢查外部連結有效性。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E18" t="str">
         <v>每半年</v>
@@ -787,10 +787,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/cp.aspx?n=77EADC52E959D9CC&amp;s=55306372EACC4F5E</v>
       </c>
       <c r="C20" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D20" t="str">
-        <v>已檢視尋職簽證頁面；含申請條件與規範說明。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E20" t="str">
         <v>每半年</v>
@@ -807,10 +807,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=A9F8A4FF82A871AC</v>
       </c>
       <c r="C21" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D21" t="str">
-        <v>已檢視數位遊牧簽證頁面；建議與中文版同步檢查停留期間與申辦條件是否一致。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E21" t="str">
         <v>每半年</v>
@@ -827,10 +827,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/cp.aspx?n=A7C836C13205092B&amp;s=85176E194E7C848A</v>
       </c>
       <c r="C22" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D22" t="str">
-        <v>已檢視永久居留頁面；含申請條件與相關法規連結。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E22" t="str">
         <v>每半年</v>
@@ -847,10 +847,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=23CD782FBC63F065</v>
       </c>
       <c r="C23" t="str">
-        <v>建議於每年度稅法修正後檢視優惠規定是否更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D23" t="str">
-        <v>已檢視租稅優惠頁面；含所得稅優惠規定，建議於稅法修正時同步更新。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E23" t="str">
         <v>每年</v>
@@ -867,10 +867,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=0751F32881BC1238</v>
       </c>
       <c r="C24" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D24" t="str">
-        <v>已檢視就業保險頁面；含外國人納保規定。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E24" t="str">
         <v>每半年</v>
@@ -887,10 +887,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=91EFE79FF3100330</v>
       </c>
       <c r="C25" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D25" t="str">
-        <v>已檢視港澳居民準用頁面；含準用規定說明。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E25" t="str">
         <v>每半年</v>
@@ -927,10 +927,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=F5696D5BB0943F84</v>
       </c>
       <c r="C27" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D27" t="str">
-        <v>已檢視關於本法Q&amp;A頁面。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E27" t="str">
         <v>每半年</v>
@@ -947,10 +947,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=5E840899B0BFD62F</v>
       </c>
       <c r="C28" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D28" t="str">
-        <v>已檢視數位遊牧簽證頁面；建議與中文版同步檢查停留期間與申辦條件是否一致。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E28" t="str">
         <v>每半年</v>
@@ -967,10 +967,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=AF240B92F67EDDCC</v>
       </c>
       <c r="C29" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D29" t="str">
-        <v>已檢視該公開頁面內容。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E29" t="str">
         <v>每半年</v>
@@ -987,10 +987,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=2715FDF194911C1A</v>
       </c>
       <c r="C30" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D30" t="str">
-        <v>已檢視教師相關工作許可頁面；含申請條件與法規連結。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E30" t="str">
         <v>每半年</v>
@@ -1007,10 +1007,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=97392D0AE9A161C6</v>
       </c>
       <c r="C31" t="str">
-        <v>外部連結 awpft.moe.gov.tw 無法連線，建議確認或移除。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D31" t="str">
-        <v>已檢視教師相關工作許可頁面；含申請條件與法規連結。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E31" t="str">
         <v>每半年</v>
@@ -1027,10 +1027,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=1345A588EFF5EB10</v>
       </c>
       <c r="C32" t="str">
-        <v>外部連結 awpft.moe.gov.tw 無法連線，建議確認或移除。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D32" t="str">
-        <v>已檢視實驗教育工作者頁面；含申請條件說明。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E32" t="str">
         <v>每半年</v>
@@ -1047,10 +1047,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=7E66E2B3F32255BB</v>
       </c>
       <c r="C33" t="str">
-        <v>建議於大學排名更新時同步檢視資格條件。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D33" t="str">
-        <v>已檢視碩士及前1,500大畢業生免2年工作經驗頁面；建議於大學排名更新時檢視。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E33" t="str">
         <v>每年</v>
@@ -1067,10 +1067,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=3CD0D7988FFB2094</v>
       </c>
       <c r="C34" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D34" t="str">
-        <v>已檢視免工作許可Q&amp;A頁面。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E34" t="str">
         <v>每半年</v>
@@ -1087,10 +1087,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=FCB4ADC7DC71311F</v>
       </c>
       <c r="C35" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D35" t="str">
-        <v>已檢視該公開頁面內容。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E35" t="str">
         <v>每半年</v>
@@ -1107,10 +1107,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=57ABC704441FFEFC</v>
       </c>
       <c r="C36" t="str">
-        <v>建議每月更新統計數據及確認申請說明是否需調整。</v>
+        <v>【建議修正】相關申辦流程或說明文件若非最新版，建議更新。</v>
       </c>
       <c r="D36" t="str">
-        <v>已檢視就業金卡頁面；含申請說明與統計資料，建議每月更新統計數據。</v>
+        <v>就業金卡頁面資訊豐富，建議持續更新申辦連結及說明。</v>
       </c>
       <c r="E36" t="str">
         <v>每季</v>
@@ -1127,10 +1127,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=4CD26A50C37651FD</v>
       </c>
       <c r="C37" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D37" t="str">
-        <v>已檢視自由藝術工作者頁面；含申請條件說明。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E37" t="str">
         <v>每半年</v>
@@ -1147,10 +1147,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=B682246C50440B1C</v>
       </c>
       <c r="C38" t="str">
-        <v>建議於大學排名更新時同步檢視資格條件。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D38" t="str">
-        <v>已檢視前200大畢業生個人工作許可頁面；建議於大學排名更新時檢視。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E38" t="str">
         <v>每年</v>
@@ -1167,10 +1167,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=CDFD615CAFDEBB84</v>
       </c>
       <c r="C39" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D39" t="str">
-        <v>已檢視僑外生延期居留免工作許可頁面。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E39" t="str">
         <v>每半年</v>
@@ -1187,10 +1187,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=407B8C2EE0358D53</v>
       </c>
       <c r="C40" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D40" t="str">
-        <v>已檢視尋職簽證頁面；含申請條件與規範說明。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E40" t="str">
         <v>每半年</v>
@@ -1207,10 +1207,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=5CBBE106F8B1013D</v>
       </c>
       <c r="C41" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D41" t="str">
-        <v>已檢視數位遊牧簽證頁面；建議與中文版同步檢查停留期間與申辦條件是否一致。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E41" t="str">
         <v>每半年</v>
@@ -1227,10 +1227,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=DEDB5D8E6867D925</v>
       </c>
       <c r="C42" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D42" t="str">
-        <v>已檢視成年子女工作相關Q&amp;A頁面。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E42" t="str">
         <v>每半年</v>
@@ -1247,10 +1247,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=EBB8A3F10FC5A3DE</v>
       </c>
       <c r="C43" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D43" t="str">
-        <v>已檢視配偶工作相關Q&amp;A頁面。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E43" t="str">
         <v>每半年</v>
@@ -1267,10 +1267,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=DAE993AC257443D5</v>
       </c>
       <c r="C44" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D44" t="str">
-        <v>已檢視永久居留頁面；含申請條件與相關法規連結。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E44" t="str">
         <v>每半年</v>
@@ -1287,10 +1287,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=ACD0BEECD2BA6F75</v>
       </c>
       <c r="C45" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D45" t="str">
-        <v>已檢視外國專業人才及眷屬申請居留Q&amp;A頁面。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E45" t="str">
         <v>每半年</v>
@@ -1307,10 +1307,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=BFBC5E30504A150B</v>
       </c>
       <c r="C46" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D46" t="str">
-        <v>已檢視永久居留頁面；含申請條件與相關法規連結。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E46" t="str">
         <v>每半年</v>
@@ -1327,10 +1327,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=9B80BB14966931D6</v>
       </c>
       <c r="C47" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D47" t="str">
-        <v>已檢視直系尊親屬探親停留Q&amp;A頁面。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E47" t="str">
         <v>每半年</v>
@@ -1347,10 +1347,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=801F18D19E0004F4</v>
       </c>
       <c r="C48" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D48" t="str">
-        <v>已檢視永久居留廢止頁面；含廢止條件說明。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E48" t="str">
         <v>每半年</v>
@@ -1367,10 +1367,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=81D383233E2C9ED0</v>
       </c>
       <c r="C49" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D49" t="str">
-        <v>已檢視身心障礙子女認定Q&amp;A頁面。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E49" t="str">
         <v>每半年</v>
@@ -1387,10 +1387,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=7CBF985CB4015A88</v>
       </c>
       <c r="C50" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D50" t="str">
-        <v>已檢視優惠待遇/社會保障Q&amp;A總覽頁面。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E50" t="str">
         <v>每半年</v>
@@ -1407,10 +1407,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=107AE5589F2D9750</v>
       </c>
       <c r="C51" t="str">
-        <v>建議於每年度稅法修正後檢視優惠規定是否更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D51" t="str">
-        <v>已檢視租稅優惠頁面；含所得稅優惠規定，建議於稅法修正時同步更新。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E51" t="str">
         <v>每年</v>
@@ -1427,10 +1427,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=DC6E79829DEC4C77</v>
       </c>
       <c r="C52" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D52" t="str">
-        <v>已檢視健保納保Q&amp;A頁面；含全民健康保險相關規定。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E52" t="str">
         <v>每半年</v>
@@ -1447,10 +1447,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=ABF276774004FE73</v>
       </c>
       <c r="C53" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D53" t="str">
-        <v>已檢視勞退新制Q&amp;A頁面；含勞工退休金新制規定。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E53" t="str">
         <v>每半年</v>
@@ -1467,10 +1467,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=6408E7BA616A7597</v>
       </c>
       <c r="C54" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D54" t="str">
-        <v>已檢視就業保險頁面；含外國人納保規定。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E54" t="str">
         <v>每半年</v>
@@ -1487,10 +1487,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=BAE173DE4EFD5162</v>
       </c>
       <c r="C55" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D55" t="str">
-        <v>已檢視教師相關工作許可頁面；含申請條件與法規連結。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E55" t="str">
         <v>每半年</v>
@@ -1507,10 +1507,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=EF091D57D8CC6928</v>
       </c>
       <c r="C56" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D56" t="str">
-        <v>已檢視教師相關工作許可頁面；含申請條件與法規連結。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E56" t="str">
         <v>每半年</v>
@@ -1527,10 +1527,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=536B49DBF970754D</v>
       </c>
       <c r="C57" t="str">
-        <v>建議每月更新就業金卡統計資料。</v>
+        <v>【建議定期更新】建議每月/季更新統計數據，並確認圖表或附件是否為最新月份。</v>
       </c>
       <c r="D57" t="str">
-        <v>已檢視統計資料頁面；含歷年就業金卡統計，建議每月更新。</v>
+        <v>頁面提供歷年統計數據，建議持續更新以反映最新人才延攬成效。</v>
       </c>
       <c r="E57" t="str">
         <v>每月</v>
@@ -1547,10 +1547,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/cp.aspx?n=CF6D2CE4909E945F&amp;s=27B3AAEEB86F1B0D</v>
       </c>
       <c r="C58" t="str">
-        <v>建議確認Talent Taiwan跨站連結正常，並檢查聯絡方式是否需要更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D58" t="str">
-        <v>已檢視聯絡窗口頁面；導引至Talent Taiwan網站，建議確認跨站連結正常。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E58" t="str">
         <v>每半年</v>
@@ -1587,10 +1587,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/SiteMap.aspx?n=6D1C61735B06594E</v>
       </c>
       <c r="C60" t="str">
-        <v>建議定期檢視內容是否需要依法規修正更新。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D60" t="str">
-        <v>已檢視網站導覽頁面；含無障礙設計說明與快速鍵。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E60" t="str">
         <v>每半年</v>

--- a/網站盤點表-中文.xlsx
+++ b/網站盤點表-中文.xlsx
@@ -447,10 +447,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Default.aspx</v>
       </c>
       <c r="C3" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議維護】首頁「最新消息」區塊目前僅顯示就業金卡統計資訊，建議增加其他類型之政策宣導訊息（如修法動態、新制上路等），以豐富首頁內容。另首頁「相關連結」區塊之外部連結（如移民署申辦窗口、Talent Taiwan等），建議定期確認連結有效性。</v>
       </c>
       <c r="D3" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>首頁呈現最新消息摘要及相關連結區塊。目前最新消息以就業金卡統計為主，內容時效性尚可（最新為115年2月資料）。相關連結包含移民署四合一申辦窗口及Talent Taiwan，連結均有效。</v>
       </c>
       <c r="E3" t="str">
         <v>每季</v>
@@ -487,10 +487,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/News.aspx?n=801CA6E93C4EF61B&amp;sms=39B785FD08C5E6BB</v>
       </c>
       <c r="C5" t="str">
-        <v>【建議維護】定期檢視過期消息是否需歸檔，並發布最新修法動態。</v>
+        <v>【建議維護】最新消息列表目前以就業金卡月度統計為主，建議增發其他議題之新聞稿或政策說明（如新制施行、子法公告等），避免內容過度集中於單一主題。另建議定期歸檔逾2年之舊消息，以維持頁面瀏覽體驗。</v>
       </c>
       <c r="D5" t="str">
-        <v>最新消息列表正常，建議持續發布相關政策宣導資訊。</v>
+        <v>最新消息頁面共列出數十則訊息，時間涵蓋107年至115年。最新一則為115年2月23日「2026年1月31日就業金卡統計」，更新頻率約每月一次。消息內容以就業金卡統計佔大多數，114年12月有修法施行公告。</v>
       </c>
       <c r="E5" t="str">
         <v>每月</v>
@@ -507,10 +507,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=E6309CCCA6ED1775</v>
       </c>
       <c r="C6" t="str">
-        <v>【建議修正】相關檔案「111年外國專業人才延攬及僱用相關法規彙編」標示(待更新)，已歷時約4年未更新，建議儘速更新為最新版本（含115年1月1日施行之修正條文）。</v>
+        <v>【建議修正】1.相關檔案區之「111年外國專業人才延攬及僱用相關法規彙編」標示「(待更新)」，已歷時約4年未更新，建議儘速更新為最新版本（含115年1月1日施行之修正條文）。2.相關連結「全國法規資料庫-所有條文」建議確認是否已連結至最新修正版本。</v>
       </c>
       <c r="D6" t="str">
-        <v>頁面說明外國人才專法立法沿革、修法重點，內文已涵蓋2025年第二次修法內容，內容正確。惟相關檔案「111年法規彙編」仍標示待更新，應更新為最新彙編版本。</v>
+        <v>頁面詳列外國人才專法立法沿革及修法重點，內文已涵蓋2025年第二次全案修正內容（含第4條、第28條、第29條分階段施行說明），法條說明完整。惟「相關檔案」區之111年法規彙編仍標示待更新，為本頁主要待改善事項。</v>
       </c>
       <c r="E6" t="str">
         <v>每半年</v>
@@ -527,10 +527,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=428F82FDFFD8D145</v>
       </c>
       <c r="C7" t="str">
-        <v>【建議檢視】建議檢視宣導素材（懶人包/摺頁）是否符合最新法規（115年施行），舊版建議標示或下架。</v>
+        <v>【建議檢視】本頁為宣導資料之分類目錄頁，下設「2025修法」、「2021修法」、「2018立法」三個子分類。建議確認是否需要新增其他宣導素材分類（如數位遊牧專區、就業金卡專區等），以利使用者查閱。</v>
       </c>
       <c r="D7" t="str">
-        <v>頁面包含各式宣導資料，建議確認內容是否與現行法規一致。</v>
+        <v>宣導資料為目錄頁，列出2025修法、2021修法、2018立法三個子項目及立法資料、宣導說明會、宣傳影片、摺頁、簡報等連結。頁面功能正常，無實質內容需檢視。</v>
       </c>
       <c r="E7" t="str">
         <v>每季</v>
@@ -547,10 +547,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=8E20BBA0AFD356E5</v>
       </c>
       <c r="C8" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議檢視】本頁提供2025年修法之7份PDF檔案（含懶人包、修法對照表等），建議確認各檔案內容是否與最終公布版本一致。另頁面文字提及「第28條及第29條定自2026年6月30日施行」，屆時應更新頁面以說明全案已全面施行。</v>
       </c>
       <c r="D8" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>頁面說明第2次全案修正之重點，包含僑外生留臺、數位遊牧簽證2年、前1500大畢業生免經驗等新制，並附7份相關PDF檔案（懶人包、修法說明、對照表等）。內容完整，已反映115年1月1日施行之修正內容。</v>
       </c>
       <c r="E8" t="str">
         <v>每季</v>
@@ -567,10 +567,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=80F66FE209D27DBA</v>
       </c>
       <c r="C9" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議檢視】本頁為子法及配套措施之總目錄頁，列出9項子分類。建議確認目錄項目名稱與子頁面標題是否一致，並於新增子法時同步更新本頁目錄。</v>
       </c>
       <c r="D9" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>子法及配套措施目錄頁，列出專業人才工作許可、特定專業人才、就業金卡、尋職簽證、數位遊牧簽證、永久居留、租稅優惠、就業保險、港澳居民準用等9大子項。頁面為純導覽頁，功能正常。</v>
       </c>
       <c r="E9" t="str">
         <v>每半年</v>
@@ -587,10 +587,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=398B18EC2B34D6FC</v>
       </c>
       <c r="C10" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議檢視】頁面說明外國專業人才工作許可係依就業服務法辦理，並提供勞動部「外國人在臺工作服務網」連結。建議確認該外部連結（ezworktaiwan.wda.gov.tw）是否持續有效，並檢視頁面所列子項目是否涵蓋115年修法新增之工作類別。</v>
       </c>
       <c r="D10" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>頁面說明一般外國專業人才工作許可依就業服務法辦理，並列出7個子項目（教師、補習班、實驗教育、前1500大、自由藝術、前200大、收費標準）。外部連結至勞動部外國人在臺工作服務網，連結有效。</v>
       </c>
       <c r="E10" t="str">
         <v>每半年</v>
@@ -607,10 +607,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=83A1B1418636FA8A</v>
       </c>
       <c r="C11" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】頁面引用外國人才專法第4條及第5條關於教師工作許可之規定，建議確認條文內容是否已更新為115年修法版本。另相關連結「各級學校申請外國教師聘僱許可及管理辦法」（law.moj.gov.tw）應確認為最新版本。</v>
       </c>
       <c r="D11" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>頁面說明外國人才專法第5條將學校教師工作許可回歸教育部主政，第4條新增「外國人才子女專班」得聘僱外籍學科教師。相關連結指向全國法規資料庫之「各級學校申請外國教師聘僱許可及管理辦法」。</v>
       </c>
       <c r="E11" t="str">
         <v>每半年</v>
@@ -627,10 +627,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=F697A748D7F5D7D9</v>
       </c>
       <c r="C12" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】頁面引用數位發展部公告「數位內容產業教學專門知識或技術之專業工作」，相關連結指向law.moda.gov.tw，該網站在先前連結檢查中回傳403，建議確認連結有效性。另請確認「短期補習班聘僱外國專業人才...審查標準」是否有配合115年修法修正。</v>
       </c>
       <c r="D12" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>頁面分兩部分說明：(1)指定具專門知識或技術之補習班，引用第4條規定及數位發展部公告；(2)外語補習班教師聘僱規定。包含2條外部法規連結（數位發展部公告、審查標準），及勞動部外國人在臺工作服務網連結。</v>
       </c>
       <c r="E12" t="str">
         <v>每半年</v>
@@ -647,10 +647,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=6B41A78BC745C459</v>
       </c>
       <c r="C13" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】頁面引用外國人才專法第4條將實驗教育工作納為專業工作，相關連結為「高級中等以下實驗教育學校及機構聘僱外國人辦法」。建議確認該辦法是否有配合115年修法進行修正，並更新頁面說明。</v>
       </c>
       <c r="D13" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>頁面說明將實驗教育三法所定之工作納為專業工作，引用第4條規定。相關連結指向全國法規資料庫「高級中等以下實驗教育學校及機構聘僱外國人辦法」，連結有效。內容簡潔。</v>
       </c>
       <c r="E13" t="str">
         <v>每半年</v>
@@ -667,10 +667,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=2369F40A62F27FA1</v>
       </c>
       <c r="C14" t="str">
-        <v>【建議檢視】建議檢視頁面連結有效性，並確認是否符合放寬後之規定。</v>
+        <v>【建議定期確認】頁面引用教育部公告之前1,500名大學名單連結（depart.moe.edu.tw），該名單通常每年更新。建議於教育部更新名單時同步確認連結是否有效，並檢視頁面說明是否需配合調整。</v>
       </c>
       <c r="D14" t="str">
-        <v>說明2025修法後放寬至前1,500大畢業生可免2年工作經驗之規定。</v>
+        <v>頁面說明2025修法後放寬至前1,500大畢業生（原為碩士以上）可免2年工作經驗之規定，引用第6條條文。相關連結指向教育部公告名單，連結有效。頁面內容已反映115年修法。</v>
       </c>
       <c r="E14" t="str">
         <v>每年</v>
@@ -687,10 +687,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=DAE420E146D0F993</v>
       </c>
       <c r="C15" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】頁面引用外國人才專法第10條關於自由藝術工作者之規定，相關連結為「外國專業人才從事藝術工作許可及管理辦法」。建議確認該管理辦法是否已配合115年修法修正（如適用對象範圍等）。</v>
       </c>
       <c r="D15" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>頁面說明外國自由藝術工作者得不經雇主申請，逕向勞動部申請許可來臺從事藝術工作，引用第10條規定。相關連結指向全國法規資料庫相關辦法，連結有效。</v>
       </c>
       <c r="E15" t="str">
         <v>每半年</v>
@@ -707,10 +707,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=C4F01439FC9E3E34</v>
       </c>
       <c r="C16" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議定期確認】頁面引用教育部公告之前200名大學名單連結（depart.moe.edu.tw），該名單依大學排名機構年度評比更新。建議於名單更新時同步確認連結有效性。另請確認頁面是否需補充115年修法對前200大個人工作許可之影響說明。</v>
       </c>
       <c r="D16" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>頁面說明外國人才專法第11條明定前200大畢業生得逕向勞動部申請個人工作許可，許可期間最長2年且不得延期。相關連結指向教育部公告名單，連結有效。</v>
       </c>
       <c r="E16" t="str">
         <v>每年</v>
@@ -727,10 +727,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=C6219BB014315D72</v>
       </c>
       <c r="C17" t="str">
-        <v>【建議定期確認】收費標準如有調整，應及時更新。</v>
+        <v>【建議定期確認】頁面列出4類工作許可之收費標準金額，金額如有調整應及時更新。另相關連結「勞動部受理外國專業人才延攬及僱用法申請案件收費標準」（law.moj.gov.tw）應確認為最新版本。</v>
       </c>
       <c r="D17" t="str">
-        <v>頁面說明各類工作許可收費標準，建議確認金額是否與勞動部公告一致。</v>
+        <v>頁面說明依外國人才專法及規費法之4類工作許可收費項目及金額：補習班教師(500元)、藝術工作(500元)、前200大個人工作許可(500元)、就業金卡(3,700元)。相關連結指向全國法規資料庫。</v>
       </c>
       <c r="E17" t="str">
         <v>每年</v>
@@ -747,10 +747,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/cp.aspx?n=D5BE87506A7C6242&amp;s=9EABA5E27250AC15</v>
       </c>
       <c r="C18" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議修正】1.頁面列出12大領域之特定專業人才認定標準，建議確認各領域公告連結是否均指向最新版本。2.頁面附有1份PDF檔案，建議確認其內容是否為115年修法後之版本。3.頁面提及「臺灣地區與大陸地區人民關係條例」連結，建議確認有效性。</v>
       </c>
       <c r="D18" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>頁面以表格呈現12大領域（科技、數位、經濟、教育、文化藝術、運動、金融、法律、建築設計、國防、環境、生技）之定義及特殊專長認定標準，另有國發會專案會商認定說明。頁面內容詳盡，已列出115年修法之領域範圍。</v>
       </c>
       <c r="E18" t="str">
         <v>每半年</v>
@@ -767,10 +767,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=C5FB0824CEC076D8</v>
       </c>
       <c r="C19" t="str">
-        <v>【建議修正】相關檔案「就業金卡申辦流程」PDF顯示日期為20211019，已超過4年未更新，應更新至現行版本（含115年修法後之申辦方式）。</v>
+        <v>【建議修正】1.相關檔案「就業金卡申辦流程」PDF日期為20211019，已超過4年未更新，應更新至現行版本（含115年修法後之申辦方式）。2.頁面連結至就業金卡官方網站（goldcard.nat.gov.tw）及移民署申辦窗口，建議定期確認連結有效性。3.建議補充115年修法對就業金卡效期（1至3年）之說明。</v>
       </c>
       <c r="D19" t="str">
-        <v>就業金卡頁面說明申辦方式，並連結至就業金卡官方網站及申辦窗口平台，惟所附申辦流程PDF日期偏舊，需更新。</v>
+        <v>就業金卡頁面引用第9條說明四證合一機制（工作許可、居留簽證、外僑居留證、重入國許可），並提供就業金卡官方網站、移民署申辦窗口、規費收費標準等6條外部連結。惟所附申辦流程PDF日期偏舊（2021年10月），為主要待改善事項。</v>
       </c>
       <c r="E19" t="str">
         <v>每季</v>
@@ -787,10 +787,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/cp.aspx?n=77EADC52E959D9CC&amp;s=55306372EACC4F5E</v>
       </c>
       <c r="C20" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】頁面引用第13條關於尋職簽證之規定，並連結至外交部領事事務局（boca.gov.tw）及全國法規資料庫之「審查及核發作業辦法」。建議確認：(1)外交部連結頁面是否已更新為115年修法後之申請須知；(2)公告限額人數是否為最新年度。</v>
       </c>
       <c r="D20" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>尋職簽證頁面分「申請及核發作業辦法」與「公告限額人數」兩部分，說明尋職簽證為3個月效期、多次入國、最長停留6個月。外部連結包含外交部說明頁及全國法規資料庫相關辦法，連結有效。</v>
       </c>
       <c r="E20" t="str">
         <v>每半年</v>
@@ -807,10 +807,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=A9F8A4FF82A871AC</v>
       </c>
       <c r="C21" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】頁面引用第14條關於數位遊牧簽證之規定（最長停留2年），相關連結指向國發會法規出版品網站（theme.ndc.gov.tw）。建議確認：(1)連結頁面是否為最新公告之一定條件；(2)115年修法施行後是否有新增配套措施需於本頁補充。</v>
       </c>
       <c r="D21" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>數位遊牧簽證頁面說明第14條規定，外國專業人才以數位方式從事遠端工作且非為我國境內雇主提供勞務者，得申請最長2年之數位遊牧簽證，本人、配偶、未成年子女及身心障礙成年子女均可申請。相關連結指向一定條件之公告。</v>
       </c>
       <c r="E21" t="str">
         <v>每半年</v>
@@ -827,10 +827,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/cp.aspx?n=A7C836C13205092B&amp;s=85176E194E7C848A</v>
       </c>
       <c r="C22" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】頁面說明永久居留之鬆綁內容（彈性計算183日、縮短申請年限等），引用第18條及第19條。建議確認：(1)頁面是否已反映115年修法對永久居留年限之調整；(2)「無不良素行認定標準」子項目是否需更新。</v>
       </c>
       <c r="D22" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>永久居留頁面分「申請永久居留相關規範」及「無不良素行認定標準」兩部分，說明外國專業人才連續居留可申請永久居留、副學士以上學位得折抵1至3年、依親親屬之永久居留條件等。內容引用第18、19、21條。</v>
       </c>
       <c r="E22" t="str">
         <v>每半年</v>
@@ -847,10 +847,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=23CD782FBC63F065</v>
       </c>
       <c r="C23" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】1.頁面附有1份PDF檔案及「外國特定專業人才減免所得稅辦法」連結，建議確認是否為115年修法後之最新版本。2.頁面提及「薪資所得超過300萬元起5年內折半課稅」，建議確認此金額門檻是否因修法有所調整。</v>
       </c>
       <c r="D23" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>租稅優惠頁面引用第22條，說明外國特定專業人才首次核准來臺工作且薪資超過300萬元者，5年內超過部分折半課稅，海外所得免計入基本所得額。外部連結包含全國法規資料庫之減免所得稅辦法及1份PDF附件。</v>
       </c>
       <c r="E23" t="str">
         <v>每年</v>
@@ -867,10 +867,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=0751F32881BC1238</v>
       </c>
       <c r="C24" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】頁面引用第25條關於永久居留者適用就業保險之規定，相關連結為「就業保險法施行細則」。建議確認連結是否為115年最新版本，並檢視頁面是否需補充115年修法對就業保險適用範圍之影響說明。</v>
       </c>
       <c r="D24" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>就業保險頁面引用第25條，說明取得永久居留之外國專業人才適用就業保險法。頁面附相關連結至全國法規資料庫「就業保險法施行細則」，連結有效。內容簡潔明確。</v>
       </c>
       <c r="E24" t="str">
         <v>每半年</v>
@@ -887,10 +887,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=91EFE79FF3100330</v>
       </c>
       <c r="C25" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】頁面引用第30條關於港澳居民準用本法之規定，相關連結為「香港澳門關係條例及相關許可辦法」。建議確認：(1)連結指向之法規是否已配合115年修法調整；(2)頁面說明是否需補充港澳居民可準用之具體條文範圍。</v>
       </c>
       <c r="D25" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>港澳居民準用頁面引用第30條及香港澳門關係條例第13條，說明港澳居民在臺從事專業工作及尋職準用本法相關規定。相關連結指向全國法規資料庫，連結有效。</v>
       </c>
       <c r="E25" t="str">
         <v>每半年</v>
@@ -907,10 +907,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=1384836FA7D2CFA6</v>
       </c>
       <c r="C26" t="str">
-        <v>【建議確認】修法後應確認Q&amp;A各子項是否已更新至115年修法內容。</v>
+        <v>【建議確認】Q&amp;A目錄頁列出4大分類（關於本法、工作/尋職/數位遊牧、停留/居留/永久居留、優惠待遇/社會保障），115年修法施行後，各子項Q&amp;A應逐一確認是否需新增或修改問答內容（特別是數位遊牧簽證2年、前1500大免經驗、僑外生免工作許可等新制）。</v>
       </c>
       <c r="D26" t="str">
-        <v>頁面分為「關於本法」及「工作/尋職/數位遊牧」等多個分類，內含多個子頁面。2025修法後應定期確認各Q&amp;A內容是否與現行規定一致。</v>
+        <v>Q&amp;A為目錄頁，分為4大分類共含15個以上子項目，涵蓋工作許可、居留、優惠待遇等主題。頁面功能正常，為各子項Q&amp;A之入口。</v>
       </c>
       <c r="E26" t="str">
         <v>每半年</v>
@@ -927,10 +927,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=F5696D5BB0943F84</v>
       </c>
       <c r="C27" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議修正】Q1回答提及「107年2月8日正式施行」，內容僅涵蓋初次立法資訊，建議補充110年第1次修法及115年第2次修法之說明，使回答涵蓋本法完整沿革。</v>
       </c>
       <c r="D27" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「關於本法」僅1則問答（Q1：為什麼要訂定本法），回答說明本法107年施行背景及政策目的。內容正確但未涵蓋後續2次修法進程，資訊較為陳舊。</v>
       </c>
       <c r="E27" t="str">
         <v>每半年</v>
@@ -947,10 +947,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=5E840899B0BFD62F</v>
       </c>
       <c r="C28" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議檢視】本頁為「工作/尋職/數位遊牧」Q&amp;A目錄頁，列出15個子項目。建議確認子項目名稱是否與115年修法後之制度名稱一致（如「成年子女工作」及「配偶工作」為115年新增規定）。</v>
       </c>
       <c r="D28" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「工作/尋職/數位遊牧」目錄頁，列出專業工作許可、補習班教師、教師、實驗教育、前1500大、不須申請工作許可、特定專業人才、就業金卡、自由藝術、前200大、僑外生免許可、尋職簽證、數位遊牧、成年子女、配偶等15個子項。</v>
       </c>
       <c r="E28" t="str">
         <v>每半年</v>
@@ -967,10 +967,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=AF240B92F67EDDCC</v>
       </c>
       <c r="C29" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q1回答說明就業服務法與外國人才專法之差異，建議確認內容是否已反映115年修法新增之工作類別（如數位遊牧等），並檢視答覆中引用之法條條號是否與修法後一致。</v>
       </c>
       <c r="D29" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「專業工作許可」含Q1（適用法規差異），說明就業服務法及外國人才專法之主要區別。內容涵蓋工作許可特別規定及新增工作類型說明。</v>
       </c>
       <c r="E29" t="str">
         <v>每半年</v>
@@ -987,10 +987,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=2715FDF194911C1A</v>
       </c>
       <c r="C30" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q1回答列出外國人月薪門檻（47,971元），建議確認此金額是否為115年最新標準。另回答中列出之雇主資格條件、外國語文教師資格等，應確認是否與現行審查標準一致。</v>
       </c>
       <c r="D30" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「短期補習班教師」含多則問答，詳列外國人資格（月薪47,971元以上、具國際教學經驗等）、雇主資格（公司法人、與國際教學機構合作等）、外語教師資格等。內容具體詳盡。</v>
       </c>
       <c r="E30" t="str">
         <v>每半年</v>
@@ -1007,10 +1007,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=97392D0AE9A161C6</v>
       </c>
       <c r="C31" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【注意】Q1回答提供之連結 https://www.awpft.moe.gov.tw/ 在先前連結檢查中回傳連線逾時，疑似失效。建議確認該教育部外國人才聘僱許可系統是否已更換網址，並更新頁面連結。</v>
       </c>
       <c r="D31" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「教師工作許可」含Q1（如何申請），說明由各級學校依「各級學校申請外國教師聘僱許可及管理辦法」向教育部申請，並附申請流程圖。外部連結 awpft.moe.gov.tw 疑似失效，為本頁主要問題。</v>
       </c>
       <c r="E31" t="str">
         <v>每半年</v>
@@ -1027,10 +1027,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=1345A588EFF5EB10</v>
       </c>
       <c r="C32" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【注意】1.Q1及Q2回答中之連結 https://www.awpft.moe.gov.tw/ 在先前檢查中回傳連線逾時，建議確認並更新。2.頁面附有1份PDF檔案，建議確認是否為115年修法後之最新版本。</v>
       </c>
       <c r="D32" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「實驗教育工作」含多則問答，說明聘僱申請系統（awpft.moe.gov.tw）、許可期間（最長3年）、收費標準（500元）、特殊情況處理等。附1份PDF附件。awpft.moe.gov.tw連結疑似失效。</v>
       </c>
       <c r="E32" t="str">
         <v>每半年</v>
@@ -1047,10 +1047,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=7E66E2B3F32255BB</v>
       </c>
       <c r="C33" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q1回答指向教育部網站查詢前1,500名大學名單，Q2列舉專門性或技術性工作類型。建議確認：(1)教育部連結是否有效且為最新名單；(2)工作類型是否與115年修法後之規定一致。</v>
       </c>
       <c r="D33" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「碩士及前1,500名大學畢業生」含多則問答，說明前1,500名大學由教育部公告、可從事之專門性或技術性工作類型（營繕、交通、財稅、不動產等）。外部連結指向教育部網站。</v>
       </c>
       <c r="E33" t="str">
         <v>每年</v>
@@ -1067,10 +1067,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=3CD0D7988FFB2094</v>
       </c>
       <c r="C34" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q1回答說明免申請工作許可之情形（政府聘請顧問、大學講座等及永久居留者），建議確認是否需補充115年修法新增之免許可情形（如僑外生延期居留期間免許可等相關說明）。</v>
       </c>
       <c r="D34" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「不須申請工作許可」含Q1，說明受政府聘請擔任顧問或研究、受大學聘僱進行講座等情形免申請工作許可，另說明永久居留者及其眷屬亦無需申請。</v>
       </c>
       <c r="E34" t="str">
         <v>每半年</v>
@@ -1087,10 +1087,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=FCB4ADC7DC71311F</v>
       </c>
       <c r="C35" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q1定義外國特定專業人才涵蓋12大領域，Q2說明申請管道。建議確認：(1)領域列舉是否與115年修法後之第4條一致（是否新增「環境」及「生技」領域）；(2)申請管道說明是否為最新流程。</v>
       </c>
       <c r="D35" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「特定專業人才工作許可」含Q1（定義）及Q2（申請管道），說明12大領域之特殊專長認定及工作許可申請方式。內容與子法及配套措施之「特定專業人才」頁面互補。</v>
       </c>
       <c r="E35" t="str">
         <v>每半年</v>
@@ -1107,10 +1107,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=57ABC704441FFEFC</v>
       </c>
       <c r="C36" t="str">
-        <v>【建議修正】相關申辦流程或說明文件若非最新版，建議更新。</v>
+        <v>【建議修正】1.頁面附有1份PDF檔案，建議確認是否與子法專區之就業金卡頁面所附為同一份（20211019版），如是則同樣需更新。2.Q&amp;A中引用之移民署申辦窗口連結（coa.immigration.gov.tw）應確認有效性。3.建議確認Q&amp;A是否已涵蓋115年修法對就業金卡效期調整之說明。</v>
       </c>
       <c r="D36" t="str">
-        <v>就業金卡頁面資訊豐富，建議持續更新申辦連結及說明。</v>
+        <v>Q&amp;A「就業金卡」含多則問答（申請方式、審核期間繳驗護照、效期延期、更換護照等），並連結至移民署「外國專業人才申辦窗口平臺」。附1份PDF檔案。內容實用，涵蓋申辦常見問題。</v>
       </c>
       <c r="E36" t="str">
         <v>每季</v>
@@ -1127,10 +1127,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=4CD26A50C37651FD</v>
       </c>
       <c r="C37" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q&amp;A列出藝術工作許可之申請管道及資格條件（表演及視覺藝術類、公播及出版藝術類），建議確認資格條件是否與現行「外國專業人才從事藝術工作許可及管理辦法」一致。</v>
       </c>
       <c r="D37" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「自由藝術工作許可」含多則問答，以表格呈現2類藝術工作（表演及視覺藝術類、公播及出版藝術類）之資格條件，說明國際獎項或工作經驗要求等。內容詳盡。</v>
       </c>
       <c r="E37" t="str">
         <v>每半年</v>
@@ -1147,10 +1147,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=B682246C50440B1C</v>
       </c>
       <c r="C38" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議定期確認】Q1指向教育部公告之前200名大學名單，Q2說明許可期間最長2年且不得延期。建議確認教育部連結是否為最新年度名單，並確認Q&amp;A是否需補充115年修法之相關說明。</v>
       </c>
       <c r="D38" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「前200名大學之畢業生」含多則問答，說明最近5年內取得前200大學士以上學位者得逕向勞動部申請個人工作許可，許可期間最長2年且不得延期。外部連結指向教育部網站。</v>
       </c>
       <c r="E38" t="str">
         <v>每年</v>
@@ -1167,10 +1167,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=CDFD615CAFDEBB84</v>
       </c>
       <c r="C39" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q1回答引用第12條說明僑外生取得副學士以上學位後延期居留期間免工作許可。建議確認此為115年修法版本之條號及內容（原條文為第7條），並檢視是否需補充更多細節說明。</v>
       </c>
       <c r="D39" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「僑外生延期居留期間免工作許可」含Q1，說明依第12條規定取得副學士以上學位之應屆畢業僑外生，於延期居留期間從事工作免申請工作許可。內容簡潔。</v>
       </c>
       <c r="E39" t="str">
         <v>每半年</v>
@@ -1187,10 +1187,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=407B8C2EE0358D53</v>
       </c>
       <c r="C40" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q2列出尋職簽證3項申請條件（月薪47,971元、畢業1年內、QS前500大），建議確認金額及條件是否與115年修法後之規定一致。另外交部連結（boca.gov.tw）應確認有效性。</v>
       </c>
       <c r="D40" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「尋職簽證」含Q1（定義：3個月效期、最長6個月）及Q2（申請條件：月薪、畢業生、QS前500大），並連結至外交部說明頁面。條件說明具體，實用性高。</v>
       </c>
       <c r="E40" t="str">
         <v>每半年</v>
@@ -1207,10 +1207,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=5CBBE106F8B1013D</v>
       </c>
       <c r="C41" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q&amp;A說明數位遊牧簽證之定義、申請條件（免簽證國、年收入等）及停留期間（每次最長2年），建議確認內容是否完整反映115年修法後之規定，特別是配偶及子女之申請資格。另外交部連結（boca.gov.tw）應確認為最新申辦說明。</v>
       </c>
       <c r="D41" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「數位遊牧簽證」含Q1（定義）、Q2（申請條件：免簽證國、年收入門檻等）等，說明每次總停留期間最長2年。外部連結指向外交部申辦說明頁面。內容已涵蓋115年修法之2年期規定。</v>
       </c>
       <c r="E41" t="str">
         <v>每半年</v>
@@ -1227,10 +1227,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=DEDB5D8E6867D925</v>
       </c>
       <c r="C42" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q1回答引用第15條及第32條關於成年子女工作許可之規定，外部連結指向勞動部外國人在臺工作服務網。建議確認：(1)條文引用是否為115年版本；(2)勞動部連結是否有效且為對應頁面。</v>
       </c>
       <c r="D42" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「成年子女工作」含多則問答，說明取得永久居留或歸化國籍之外國專業人才，其成年子女符合居留條件者得逕向勞動部申請個人工作許可。外部連結指向勞動部服務網，連結有效。</v>
       </c>
       <c r="E42" t="str">
         <v>每半年</v>
@@ -1247,10 +1247,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=EBB8A3F10FC5A3DE</v>
       </c>
       <c r="C43" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q&amp;A引用第15條及第32條說明配偶工作許可規定（限外國特定專業人才及高級專業人才之配偶），建議確認條文引用是否為115年修法版本，並檢視應備文件清單是否需更新。</v>
       </c>
       <c r="D43" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「配偶工作」含Q1（規範）及Q2（應備文件），說明外國特定專業人才及高級專業人才之配偶經許可依親居留者，得逕向勞動部申請工作許可。列出具體應備文件清單。</v>
       </c>
       <c r="E43" t="str">
         <v>每半年</v>
@@ -1267,10 +1267,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=DAE993AC257443D5</v>
       </c>
       <c r="C44" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議檢視】本頁為Q&amp;A「停留/居留/永久居留」目錄頁，列出5個子項目。建議確認子項目名稱是否與115年修法後之制度名稱一致。</v>
       </c>
       <c r="D44" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「停留/居留/永久居留」目錄頁，列出外國專業人才及眷屬申請居留、永久居留、直系尊親屬探親停留、永久居留廢止、身心障礙子女認定等5個子項。頁面為純導覽頁。</v>
       </c>
       <c r="E44" t="str">
         <v>每半年</v>
@@ -1287,10 +1287,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=ACD0BEECD2BA6F75</v>
       </c>
       <c r="C45" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q&amp;A說明就業金卡持有者之外籍家人申請居留方式及所需文件（護照、親屬證明、照片、居留證費用等），並連結至移民署網站。建議確認：(1)居留證費用金額是否為最新；(2)移民署連結（immigration.gov.tw）是否有效。</v>
       </c>
       <c r="D45" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「外國專業人才及眷屬申請居留」含多則問答，詳列就業金卡持有者家屬之居留申請文件（護照、親屬證明、照片、就業金卡影本等）及費用。外部連結2條指向移民署相關頁面。</v>
       </c>
       <c r="E45" t="str">
         <v>每半年</v>
@@ -1307,10 +1307,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=BFBC5E30504A150B</v>
       </c>
       <c r="C46" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q&amp;A說明就業金卡持有者申請永久居留之條件（滿3年、平均每年183日等），建議確認：(1)條件是否已反映115年修法對居留年限之調整；(2)是否需補充非金卡持有者之永久居留說明。</v>
       </c>
       <c r="D46" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「永久居留」含多則問答，說明就業金卡持有者需滿3年、平均每年居住183日、品行端正、無犯罪紀錄等條件。Q2進一步說明非金卡持有之外國特定專業人才之永久居留年限。</v>
       </c>
       <c r="E46" t="str">
         <v>每半年</v>
@@ -1327,10 +1327,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=9B80BB14966931D6</v>
       </c>
       <c r="C47" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q&amp;A說明直系尊親屬探親停留簽證之申請方式（向駐外館處申請）及所需文件，外部連結指向外交部（boca.gov.tw）。建議確認：(1)連結是否有效；(2)115年修法對探親停留期間（最長1年、可延期免出國）之說明是否完整。</v>
       </c>
       <c r="D47" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「直系尊親屬探親停留」含多則問答，說明外國特定/高級專業人才之直系尊親屬申請探親停留簽證之流程、文件及費用。外部連結指向外交部申辦說明。Q&amp;A涵蓋眷屬能否申請等常見疑問。</v>
       </c>
       <c r="E47" t="str">
         <v>每半年</v>
@@ -1347,10 +1347,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=801F18D19E0004F4</v>
       </c>
       <c r="C48" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q1回答說明「出國5年以上未曾入境始註銷永久居留證」，建議確認此為115年修法後之第21條規定，並檢視是否需補充其他可能導致永久居留廢止之情形。</v>
       </c>
       <c r="D48" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「永久居留廢止」僅Q1一則，回答簡潔說明出國5年以上未曾入境者將被廢止永久居留許可並註銷外僑永久居留證。內容正確。</v>
       </c>
       <c r="E48" t="str">
         <v>每半年</v>
@@ -1367,10 +1367,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=81D383233E2C9ED0</v>
       </c>
       <c r="C49" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q&amp;A說明「因身心障礙無法自理生活」之認定標準（巴氏量表30分以下等），建議確認：(1)認定標準是否與115年修法後之規定一致；(2)是否需補充國內醫療院所評估之流程說明。</v>
       </c>
       <c r="D49" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「身心障礙子女認定」含Q1（認定文件：國籍國診斷證明、巴氏量表30分以下）及Q2（國外無法開立時之替代方式），說明具體認定標準及駐外館處驗證要求。</v>
       </c>
       <c r="E49" t="str">
         <v>每半年</v>
@@ -1387,10 +1387,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=7CBF985CB4015A88</v>
       </c>
       <c r="C50" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議檢視】本頁為Q&amp;A「優惠待遇/社會保障」目錄頁，列出6個子項目。建議確認是否需因應115年修法新增子項（如第28條身心障礙照顧服務、第29條長照服務等，定自2026年6月30日施行）。</v>
       </c>
       <c r="D50" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「優惠待遇/社會保障」目錄頁，列出租稅優惠、健保納保、勞退新制、就業保險、教師及研究人員退休、園區實中雙語部教師退休保障等6個子項。頁面為純導覽頁。</v>
       </c>
       <c r="E50" t="str">
         <v>每半年</v>
@@ -1407,10 +1407,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=107AE5589F2D9750</v>
       </c>
       <c r="C51" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q&amp;A內容豐富（含總則、僑外資事業、個人工作許可等分類），頁面附2份PDF檔案。建議確認：(1)Q&amp;A引用之條號是否已更新為115年修法版本（原第9條改為第22條等）；(2)所附PDF是否為最新版本。</v>
       </c>
       <c r="D51" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「租稅優惠」含大量問答，以「總則」、「僑外資事業」、「個人工作許可」等分類說明租稅優惠之法令依據、適用條件、申報方式等。引用外國人才專法第22條（原第9條）及減免所得稅辦法。附2份PDF附件。</v>
       </c>
       <c r="E51" t="str">
         <v>每年</v>
@@ -1427,10 +1427,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=DC6E79829DEC4C77</v>
       </c>
       <c r="C52" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q&amp;A說明外國專業人才健保參加資格及免6個月等待期之規定，建議確認：(1)內容是否已反映115年修法版本（第23條）；(2)雇主及自營業主身分之適用說明是否完整。</v>
       </c>
       <c r="D52" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「健保納保」含多則問答，說明全民健保之參加資格、加保類別、免6個月等待期之規定及眷屬納保方式。回答具體，涵蓋受聘僱、雇主/自營業主等不同身分之適用情形。</v>
       </c>
       <c r="E52" t="str">
         <v>每半年</v>
@@ -1447,10 +1447,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=ABF276774004FE73</v>
       </c>
       <c r="C53" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q&amp;A附有1份PDF檔案，外部連結包含勞保局e化系統及全球資訊網。建議確認：(1)勞退新制說明是否已更新為115年修法版本（第24條）；(2)所附PDF及外部連結是否有效。</v>
       </c>
       <c r="D53" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「勞退新制」含多則問答，說明雇主按月提繳6%、勞工自願提繳6%、適用時程（107年施行起）、請領方式等。外部連結包含勞保局e化服務系統及全球資訊網。附1份PDF附件。</v>
       </c>
       <c r="E53" t="str">
         <v>每半年</v>
@@ -1467,10 +1467,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=6408E7BA616A7597</v>
       </c>
       <c r="C54" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q&amp;A引用115年修法第25條，說明永久居留者適用就業保險。外部連結包含勞保局全球資訊網，附1份PDF檔案。建議確認所附PDF及連結是否為最新版本，並檢視Q&amp;A是否已涵蓋115年新制之重要變更。</v>
       </c>
       <c r="D54" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「就業保險」含多則問答，明確引用「115年1月1日修正施行之第25條」，說明取得永久居留之三類外國人才自115年起為就業保險適用對象。外部連結指向勞保局。附1份PDF附件。已反映115年修法。</v>
       </c>
       <c r="E54" t="str">
         <v>每半年</v>
@@ -1487,10 +1487,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=BAE173DE4EFD5162</v>
       </c>
       <c r="C55" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q1回答引用第26條說明教師及研究人員退休規定（準用公立學校教職員退休資遣撫卹條例），建議確認條文引用是否為115年修法版本，並檢視永久居留者得選擇一次退休金或月退休金之說明是否完整。</v>
       </c>
       <c r="D55" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「教師及研究人員退休」含Q1，說明外國專業人才擔任公立學校教師、政府機關研究人員之退休事項準用公立學校教職員退休資遣撫卹條例，取得永久居留者得選擇支領方式。</v>
       </c>
       <c r="E55" t="str">
         <v>每半年</v>
@@ -1507,10 +1507,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=EF091D57D8CC6928</v>
       </c>
       <c r="C56" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】Q1回答引用第27條說明園區實中雙語部教師之退休保障準用公立學校教師規定，建議確認條文引用是否為115年修法版本。此為115年新增條文，應確保內容準確。</v>
       </c>
       <c r="D56" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>Q&amp;A「園區實中雙語部教師退休保障」含Q1，回答確認科學園區國立實驗高中雙語部外國教師在退休、資遣、撫卹、離職退費等事項上準用公立學校教師規定。此為115年修法新增之第27條。</v>
       </c>
       <c r="E56" t="str">
         <v>每半年</v>
@@ -1527,10 +1527,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/Content_List.aspx?n=536B49DBF970754D</v>
       </c>
       <c r="C57" t="str">
-        <v>【建議定期更新】建議每月/季更新統計數據，並確認圖表或附件是否為最新月份。</v>
+        <v>【建議定期更新】統計資料頁面以就業金卡月度統計為主，最新資料為2026年1月31日。建議：(1)每月發布最新統計數據；(2)考慮增加其他面向之統計（如各類工作許可核發數、永久居留核發數等），以全面呈現攬才成效。</v>
       </c>
       <c r="D57" t="str">
-        <v>頁面提供歷年統計數據，建議持續更新以反映最新人才延攬成效。</v>
+        <v>統計資料頁面列出2018年至2026年各月之就業金卡統計資料，按年度分類。最新資料為2026年1月，更新頻率約每月一次。統計內容目前僅涵蓋就業金卡，未包含其他人才延攬指標。</v>
       </c>
       <c r="E57" t="str">
         <v>每月</v>
@@ -1547,10 +1547,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/cp.aspx?n=CF6D2CE4909E945F&amp;s=27B3AAEEB86F1B0D</v>
       </c>
       <c r="C58" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議確認】頁面導引使用者至Talent Taiwan網站（talent.nat.gov.tw）查詢就業金卡、工作許可、簽證、居留等問題。建議確認：(1)Talent Taiwan連結是否有效；(2)是否需於本頁增列各主管機關之直接聯絡方式（如移民署、勞動部等服務專線）。</v>
       </c>
       <c r="D58" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>聯絡窗口頁面引導使用者至Talent Taiwan網站查看詳細申辦資訊，並提供「聯絡我們」留言管道。頁面未直接列出電話或Email等聯絡資訊，採轉介方式。</v>
       </c>
       <c r="E58" t="str">
         <v>每半年</v>
@@ -1587,10 +1587,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/SiteMap.aspx?n=6D1C61735B06594E</v>
       </c>
       <c r="C60" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議檢視】網站導覽頁面列出無障礙設計說明及快速鍵設定（Alt+U/C/L/Z），並提供完整站內架構樹狀圖。建議於網站架構變更時同步更新導覽頁，確保各連結均指向正確頁面。</v>
       </c>
       <c r="D60" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>網站導覽頁面說明無障礙設計原則（上方功能區、中央內容區、左方導覽區、下方選單區）及快速鍵設定，並以樹狀結構列出完整網站架構（含所有子頁連結）。</v>
       </c>
       <c r="E60" t="str">
         <v>每半年</v>
